--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>事件ID</t>
   </si>
@@ -1439,8 +1439,8 @@
       <c r="U2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>26</v>
+      <c r="V2" s="7">
+        <v>46213.0470833333</v>
       </c>
     </row>
   </sheetData>

--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -10,7 +10,7 @@
     <sheet name="事件表" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">事件表!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">事件表!$A$1:$V$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>事件ID</t>
   </si>
@@ -83,176 +83,73 @@
     <t>设备来源</t>
   </si>
   <si>
-    <t>外网IP地址</t>
-  </si>
-  <si>
-    <t>域名</t>
-  </si>
-  <si>
-    <t>文件</t>
-  </si>
-  <si>
     <t>推送状态</t>
   </si>
   <si>
     <t>完成时间</t>
   </si>
   <si>
+    <t>incident-6b352a72-af84-4d32-b70c-2ef2b6610af8</t>
+  </si>
+  <si>
+    <t>主机存在Chopper 2014版PHP Webshell上传</t>
+  </si>
+  <si>
+    <t>10.247.205.114</t>
+  </si>
+  <si>
+    <t>主机失陷活动（C2外联）</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>中危</t>
+  </si>
+  <si>
+    <t>处置完成</t>
+  </si>
+  <si>
+    <t>漏洞利用</t>
+  </si>
+  <si>
+    <t>WebShell管理工具</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>中国华能集团有限公司福建分公司</t>
+  </si>
+  <si>
+    <t>129.37.235.168</t>
+  </si>
+  <si>
+    <t>1.1.1.1</t>
+  </si>
+  <si>
+    <t>STA (86A45542)</t>
+  </si>
+  <si>
+    <t>已推送</t>
+  </si>
+  <si>
+    <t>incident-4b352a72-af84-4d32-b70c-2ef2b6610af8</t>
+  </si>
+  <si>
+    <t>真实攻击成功</t>
+  </si>
+  <si>
+    <t>后门攻击事件</t>
+  </si>
+  <si>
     <t>incident-5b352a72-af84-4d32-b70c-2ef2b6610af8</t>
   </si>
   <si>
-    <t>主机存在Chopper 2014版PHP Webshell上传</t>
-  </si>
-  <si>
-    <t>10.250.58.62</t>
-  </si>
-  <si>
-    <t>主机失陷活动</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>中危</t>
-  </si>
-  <si>
-    <t>处置完成</t>
-  </si>
-  <si>
-    <t>漏洞利用</t>
-  </si>
-  <si>
-    <t>WebShell管理工具</t>
-  </si>
-  <si>
-    <t>成功</t>
-  </si>
-  <si>
-    <t>中国华能集团有限公司福建分公司</t>
-  </si>
-  <si>
-    <t>129.37.235.168</t>
-  </si>
-  <si>
-    <t>1.1.1.1</t>
-  </si>
-  <si>
-    <t>STA (86A45542)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>234.37.138.166</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>171.176.77.133</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>dcwrayvajwzzw.co</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>bnssyeoqps1234.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>phishing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>qq-1319693778.cos.ap-nanjing.myqcloud.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑）</t>
-    </r>
-  </si>
-  <si>
-    <t>已推送</t>
+    <t>病毒木马活动（C2外联）</t>
+  </si>
+  <si>
+    <t>木马事件</t>
   </si>
 </sst>
 </file>
@@ -282,12 +179,25 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -299,13 +209,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -448,12 +351,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -792,152 +689,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -948,22 +845,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1285,8 +1183,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26.2777777777778" customWidth="1"/>
     <col min="2" max="2" width="26.4444444444444" customWidth="1"/>
@@ -1307,7 +1205,7 @@
     <col min="22" max="22" width="19.7037037037037" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:22">
+    <row r="1" ht="32" customHeight="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1359,92 +1257,528 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:19">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:22">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="9">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L2" s="9">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="7">
+      <c r="P2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="9">
         <v>46213.0470833333</v>
       </c>
-      <c r="L2" s="7">
-        <v>46213.8893981481</v>
-      </c>
-      <c r="M2" s="3" t="s">
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:19">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="9">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L3" s="9">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="R3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="8" t="s">
+      <c r="S3" s="9">
+        <v>46213.0470833333</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:19">
+      <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U2" s="9" t="s">
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="7">
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="9">
         <v>46213.0470833333</v>
       </c>
+      <c r="L4" s="9">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" s="9">
+        <v>46213.0470833333</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:19">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="9"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:19">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="9"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:19">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="9"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:19">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="9"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:19">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="9"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:19">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="9"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:19">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="9"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:19">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="9"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:19">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="9"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:19">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="9"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:19">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="9"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:19">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="9"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:19">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="9"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:19">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="9"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="9"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:19">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V2">
+  <autoFilter ref="A1:V20">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>事件ID</t>
   </si>
@@ -89,7 +89,7 @@
     <t>完成时间</t>
   </si>
   <si>
-    <t>incident-6b352a72-af84-4d32-b70c-2ef2b6610af8</t>
+    <t>incident-5c64c252-ce25-4584-bddf-eba401241a00</t>
   </si>
   <si>
     <t>主机存在Chopper 2014版PHP Webshell上传</t>
@@ -98,7 +98,7 @@
     <t>10.247.205.114</t>
   </si>
   <si>
-    <t>主机失陷活动（C2外联）</t>
+    <t>病毒木马活动（C2外联）</t>
   </si>
   <si>
     <t>-</t>
@@ -110,7 +110,7 @@
     <t>处置完成</t>
   </si>
   <si>
-    <t>漏洞利用</t>
+    <t>木马事件</t>
   </si>
   <si>
     <t>WebShell管理工具</t>
@@ -132,24 +132,6 @@
   </si>
   <si>
     <t>已推送</t>
-  </si>
-  <si>
-    <t>incident-4b352a72-af84-4d32-b70c-2ef2b6610af8</t>
-  </si>
-  <si>
-    <t>真实攻击成功</t>
-  </si>
-  <si>
-    <t>后门攻击事件</t>
-  </si>
-  <si>
-    <t>incident-5b352a72-af84-4d32-b70c-2ef2b6610af8</t>
-  </si>
-  <si>
-    <t>病毒木马活动（C2外联）</t>
-  </si>
-  <si>
-    <t>木马事件</t>
   </si>
 </sst>
 </file>
@@ -186,14 +168,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -846,14 +828,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1274,19 +1256,19 @@
       <c r="C2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>26</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -1324,132 +1306,35 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:19">
-      <c r="A3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="9">
-        <v>46213.0470833333</v>
-      </c>
-      <c r="L3" s="9">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="9">
-        <v>46213.0470833333</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:19">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="9">
-        <v>46213.0470833333</v>
-      </c>
-      <c r="L4" s="9">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" s="9">
-        <v>46213.0470833333</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="9"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="3"/>
       <c r="J5" s="8"/>
       <c r="K5" s="9"/>
@@ -1466,11 +1351,11 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="3"/>
       <c r="J6" s="8"/>
       <c r="K6" s="9"/>
@@ -1487,11 +1372,11 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="3"/>
       <c r="J7" s="8"/>
       <c r="K7" s="9"/>
@@ -1510,9 +1395,9 @@
       <c r="C8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="3"/>
       <c r="J8" s="8"/>
       <c r="K8" s="9"/>
@@ -1529,10 +1414,10 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="8"/>
@@ -1550,11 +1435,11 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="3"/>
       <c r="J10" s="8"/>
       <c r="K10" s="9"/>
@@ -1571,11 +1456,11 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="3"/>
       <c r="J11" s="8"/>
       <c r="K11" s="9"/>
@@ -1592,11 +1477,11 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="7"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="3"/>
       <c r="J12" s="8"/>
       <c r="K12" s="9"/>
@@ -1613,11 +1498,11 @@
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="5"/>
       <c r="I13" s="3"/>
       <c r="J13" s="8"/>
       <c r="K13" s="9"/>
@@ -1636,9 +1521,9 @@
       <c r="C14" s="4"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="7"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="3"/>
       <c r="J14" s="8"/>
       <c r="K14" s="9"/>
@@ -1655,11 +1540,11 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="3"/>
       <c r="J15" s="8"/>
       <c r="K15" s="9"/>
@@ -1676,10 +1561,10 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="8"/>
@@ -1697,11 +1582,11 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="3"/>
       <c r="J17" s="8"/>
       <c r="K17" s="9"/>
@@ -1718,11 +1603,11 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="3"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
@@ -1739,11 +1624,11 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="3"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
@@ -1762,9 +1647,9 @@
       <c r="C20" s="4"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="7"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="3"/>
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>

--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="40">
   <si>
     <t>事件ID</t>
   </si>
@@ -98,7 +98,7 @@
     <t>10.247.205.114</t>
   </si>
   <si>
-    <t>病毒木马活动（C2外联）</t>
+    <t>123活动</t>
   </si>
   <si>
     <t>-</t>
@@ -107,31 +107,49 @@
     <t>中危</t>
   </si>
   <si>
+    <t>处置中</t>
+  </si>
+  <si>
+    <t>漏洞利用</t>
+  </si>
+  <si>
+    <t>WebShell管理工具</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>中国华能集团有限公司福建分公司</t>
+  </si>
+  <si>
+    <t>129.37.235.168</t>
+  </si>
+  <si>
+    <t>1.1.1.1</t>
+  </si>
+  <si>
+    <t>STA (86A45542)</t>
+  </si>
+  <si>
+    <t>已推送</t>
+  </si>
+  <si>
+    <t>incident-5c64c252-ce26-4584-bddf-eba401241a00</t>
+  </si>
+  <si>
     <t>处置完成</t>
   </si>
   <si>
-    <t>木马事件</t>
-  </si>
-  <si>
-    <t>WebShell管理工具</t>
-  </si>
-  <si>
-    <t>成功</t>
-  </si>
-  <si>
-    <t>中国华能集团有限公司福建分公司</t>
-  </si>
-  <si>
-    <t>129.37.235.168</t>
-  </si>
-  <si>
-    <t>1.1.1.1</t>
-  </si>
-  <si>
-    <t>STA (86A45542)</t>
-  </si>
-  <si>
-    <t>已推送</t>
+    <t>incident-5c64c252-ce27-4584-bddf-eba401241a00</t>
+  </si>
+  <si>
+    <t>已遏制</t>
+  </si>
+  <si>
+    <t>待处置</t>
+  </si>
+  <si>
+    <t>已忽略</t>
   </si>
 </sst>
 </file>
@@ -816,7 +834,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -832,6 +850,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1274,13 +1295,13 @@
       <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M2" s="3" t="s">
@@ -1298,75 +1319,246 @@
       <c r="Q2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="10">
         <v>46213.0470833333</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:19">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="9"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:19">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="9"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:19">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+    <row r="3" customFormat="1" ht="24" customHeight="1" spans="1:19">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="10">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L3" s="10">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="10">
+        <v>46213.0470833333</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="24" customHeight="1" spans="1:19">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="10">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L4" s="10">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" s="10">
+        <v>46213.0470833333</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:19">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="10">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L5" s="10">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" s="10">
+        <v>46213.0470833333</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:19">
+      <c r="A6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="9"/>
+      <c r="F6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="10">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L6" s="10">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="10">
+        <v>46213.0470833333</v>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:19">
       <c r="A7" s="3"/>
@@ -1375,19 +1567,19 @@
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="10"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:19">
       <c r="A8" s="3"/>
@@ -1396,19 +1588,19 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="5"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="10"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:19">
       <c r="A9" s="3"/>
@@ -1417,19 +1609,19 @@
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="7"/>
+      <c r="G9" s="8"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="9"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="10"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:19">
       <c r="A10" s="3"/>
@@ -1438,19 +1630,19 @@
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="8"/>
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="9"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="10"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:19">
       <c r="A11" s="3"/>
@@ -1459,19 +1651,19 @@
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="7"/>
+      <c r="G11" s="8"/>
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="9"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="10"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:19">
       <c r="A12" s="3"/>
@@ -1480,19 +1672,19 @@
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="5"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="9"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="10"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:19">
       <c r="A13" s="3"/>
@@ -1501,19 +1693,19 @@
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="5"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="9"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="10"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:19">
       <c r="A14" s="3"/>
@@ -1522,19 +1714,19 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="7"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="5"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="9"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="10"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:19">
       <c r="A15" s="3"/>
@@ -1543,19 +1735,19 @@
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="7"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="5"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="9"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="10"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:19">
       <c r="A16" s="3"/>
@@ -1564,19 +1756,19 @@
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="9"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="10"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:19">
       <c r="A17" s="3"/>
@@ -1585,19 +1777,19 @@
       <c r="D17" s="5"/>
       <c r="E17" s="3"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="5"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="9"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="10"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:19">
       <c r="A18" s="3"/>
@@ -1606,19 +1798,19 @@
       <c r="D18" s="5"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="7"/>
+      <c r="G18" s="8"/>
       <c r="H18" s="5"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="9"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="10"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:19">
       <c r="A19" s="3"/>
@@ -1627,19 +1819,19 @@
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="7"/>
+      <c r="G19" s="8"/>
       <c r="H19" s="5"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="9"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="10"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:19">
       <c r="A20" s="3"/>
@@ -1648,19 +1840,19 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="7"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="5"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="9"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V20">

--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="41">
   <si>
     <t>事件ID</t>
   </si>
@@ -89,6 +89,15 @@
     <t>完成时间</t>
   </si>
   <si>
+    <t>外网IP地址</t>
+  </si>
+  <si>
+    <t>域名</t>
+  </si>
+  <si>
+    <t>文件</t>
+  </si>
+  <si>
     <t>incident-5c64c252-ce25-4584-bddf-eba401241a00</t>
   </si>
   <si>
@@ -98,7 +107,7 @@
     <t>10.247.205.114</t>
   </si>
   <si>
-    <t>123活动</t>
+    <t>主机失陷活动</t>
   </si>
   <si>
     <t>-</t>
@@ -107,10 +116,10 @@
     <t>中危</t>
   </si>
   <si>
-    <t>处置中</t>
-  </si>
-  <si>
-    <t>漏洞利用</t>
+    <t>处置完成</t>
+  </si>
+  <si>
+    <t>漏12</t>
   </si>
   <si>
     <t>WebShell管理工具</t>
@@ -134,22 +143,38 @@
     <t>已推送</t>
   </si>
   <si>
+    <r>
+      <t>45.33.32.156</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（黑）</t>
+    </r>
+  </si>
+  <si>
     <t>incident-5c64c252-ce26-4584-bddf-eba401241a00</t>
   </si>
   <si>
-    <t>处置完成</t>
+    <r>
+      <t>漏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
   </si>
   <si>
     <t>incident-5c64c252-ce27-4584-bddf-eba401241a00</t>
-  </si>
-  <si>
-    <t>已遏制</t>
-  </si>
-  <si>
-    <t>待处置</t>
-  </si>
-  <si>
-    <t>已忽略</t>
   </si>
 </sst>
 </file>
@@ -834,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -855,6 +880,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -867,6 +895,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1186,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26.2777777777778" customWidth="1"/>
@@ -1208,7 +1237,7 @@
     <col min="22" max="22" width="19.7037037037037" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:19">
+    <row r="1" ht="32" customHeight="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,298 +1295,337 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:19">
+    <row r="2" ht="24" customHeight="1" spans="1:22">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L2" s="11">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="24" customHeight="1" spans="1:22">
+      <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="10">
+      <c r="H3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="11">
         <v>46213.0470833333</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L3" s="11">
         <v>46213.8893981482</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="24" customHeight="1" spans="1:21">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="J4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="K4" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L4" s="11">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:22">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L5" s="11">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="N5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="10">
+      <c r="O5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" s="11">
         <v>46213.0470833333</v>
       </c>
+      <c r="T5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" customFormat="1" ht="24" customHeight="1" spans="1:19">
-      <c r="A3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="3" t="s">
+    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:20">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="10">
-        <v>46213.0470833333</v>
-      </c>
-      <c r="L3" s="10">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="10">
-        <v>46213.0470833333</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="24" customHeight="1" spans="1:19">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="10">
-        <v>46213.0470833333</v>
-      </c>
-      <c r="L4" s="10">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" s="10">
-        <v>46213.0470833333</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:19">
-      <c r="A5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="10">
-        <v>46213.0470833333</v>
-      </c>
-      <c r="L5" s="10">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S5" s="10">
-        <v>46213.0470833333</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:19">
-      <c r="A6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="11">
+        <v>46213.0470833333</v>
+      </c>
+      <c r="L6" s="11">
+        <v>46213.8893981482</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="10">
+      <c r="Q6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" s="11">
         <v>46213.0470833333</v>
       </c>
-      <c r="L6" s="10">
-        <v>46213.8893981482</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" s="10">
-        <v>46213.0470833333</v>
+      <c r="T6" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:19">
@@ -1567,19 +1635,19 @@
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="8"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="10"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="11"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:19">
       <c r="A8" s="3"/>
@@ -1588,19 +1656,19 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="8"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="5"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="10"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="11"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:19">
       <c r="A9" s="3"/>
@@ -1609,19 +1677,19 @@
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="8"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="10"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="11"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:19">
       <c r="A10" s="3"/>
@@ -1630,19 +1698,19 @@
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="8"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="10"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="11"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:19">
       <c r="A11" s="3"/>
@@ -1651,19 +1719,19 @@
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="8"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="10"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="11"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:19">
       <c r="A12" s="3"/>
@@ -1672,19 +1740,19 @@
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="8"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="5"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="10"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="11"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:19">
       <c r="A13" s="3"/>
@@ -1693,19 +1761,19 @@
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="8"/>
+      <c r="G13" s="9"/>
       <c r="H13" s="5"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="10"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="11"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:19">
       <c r="A14" s="3"/>
@@ -1714,19 +1782,19 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="8"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="5"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="10"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="11"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:19">
       <c r="A15" s="3"/>
@@ -1735,19 +1803,19 @@
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="8"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="5"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="10"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="11"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:19">
       <c r="A16" s="3"/>
@@ -1756,19 +1824,19 @@
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="8"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="10"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="11"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:19">
       <c r="A17" s="3"/>
@@ -1777,19 +1845,19 @@
       <c r="D17" s="5"/>
       <c r="E17" s="3"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="8"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="5"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="10"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="11"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:19">
       <c r="A18" s="3"/>
@@ -1798,19 +1866,19 @@
       <c r="D18" s="5"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="8"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="5"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="10"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="11"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:19">
       <c r="A19" s="3"/>
@@ -1819,19 +1887,19 @@
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="8"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="5"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="10"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="11"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:19">
       <c r="A20" s="3"/>
@@ -1840,19 +1908,19 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="5"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="10"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V20">

--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="39">
   <si>
     <t>事件ID</t>
   </si>
@@ -116,10 +116,10 @@
     <t>中危</t>
   </si>
   <si>
-    <t>处置完成</t>
-  </si>
-  <si>
-    <t>漏12</t>
+    <t>处置中</t>
+  </si>
+  <si>
+    <t>漏洞利用</t>
   </si>
   <si>
     <t>WebShell管理工具</t>
@@ -143,35 +143,7 @@
     <t>已推送</t>
   </si>
   <si>
-    <r>
-      <t>45.33.32.156</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（黑）</t>
-    </r>
-  </si>
-  <si>
     <t>incident-5c64c252-ce26-4584-bddf-eba401241a00</t>
-  </si>
-  <si>
-    <r>
-      <t>漏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12</t>
-    </r>
   </si>
   <si>
     <t>incident-5c64c252-ce27-4584-bddf-eba401241a00</t>
@@ -859,7 +831,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -880,9 +852,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -895,7 +864,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1327,19 +1298,19 @@
       <c r="G2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M2" s="3" t="s">
@@ -1357,22 +1328,20 @@
       <c r="Q2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="T2" s="13" t="s">
-        <v>37</v>
-      </c>
+      <c r="T2" s="12"/>
       <c r="V2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>23</v>
@@ -1392,19 +1361,19 @@
       <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>39</v>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M3" s="3" t="s">
@@ -1422,15 +1391,13 @@
       <c r="Q3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="T3" s="13" t="s">
-        <v>37</v>
-      </c>
+      <c r="T3" s="12"/>
       <c r="U3" t="s">
         <v>26</v>
       </c>
@@ -1440,7 +1407,7 @@
     </row>
     <row r="4" customFormat="1" ht="24" customHeight="1" spans="1:21">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -1460,19 +1427,19 @@
       <c r="G4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>39</v>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M4" s="3" t="s">
@@ -1490,22 +1457,20 @@
       <c r="Q4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="T4" s="13" t="s">
-        <v>37</v>
-      </c>
+      <c r="T4" s="12"/>
       <c r="U4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>23</v>
@@ -1525,19 +1490,19 @@
       <c r="G5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>39</v>
+      <c r="H5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M5" s="3" t="s">
@@ -1555,22 +1520,20 @@
       <c r="Q5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="T5" s="13" t="s">
-        <v>37</v>
-      </c>
+      <c r="T5" s="12"/>
       <c r="V5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:20">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>23</v>
@@ -1588,19 +1551,19 @@
       <c r="G6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>39</v>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>46213.8893981482</v>
       </c>
       <c r="M6" s="3" t="s">
@@ -1618,15 +1581,13 @@
       <c r="Q6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="R6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="10">
         <v>46213.0470833333</v>
       </c>
-      <c r="T6" s="13" t="s">
-        <v>37</v>
-      </c>
+      <c r="T6" s="12"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:19">
       <c r="A7" s="3"/>
@@ -1635,19 +1596,19 @@
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="9"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="10"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:19">
       <c r="A8" s="3"/>
@@ -1656,19 +1617,19 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="9"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="5"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="10"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:19">
       <c r="A9" s="3"/>
@@ -1677,19 +1638,19 @@
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="9"/>
+      <c r="G9" s="8"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="10"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:19">
       <c r="A10" s="3"/>
@@ -1698,19 +1659,19 @@
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="9"/>
+      <c r="G10" s="8"/>
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="10"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:19">
       <c r="A11" s="3"/>
@@ -1719,19 +1680,19 @@
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="9"/>
+      <c r="G11" s="8"/>
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="10"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:19">
       <c r="A12" s="3"/>
@@ -1740,19 +1701,19 @@
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="9"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="5"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="10"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:19">
       <c r="A13" s="3"/>
@@ -1761,19 +1722,19 @@
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="9"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="5"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="10"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:19">
       <c r="A14" s="3"/>
@@ -1782,19 +1743,19 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="9"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="5"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="10"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:19">
       <c r="A15" s="3"/>
@@ -1803,19 +1764,19 @@
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="9"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="5"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="10"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:19">
       <c r="A16" s="3"/>
@@ -1824,19 +1785,19 @@
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="9"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="10"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:19">
       <c r="A17" s="3"/>
@@ -1845,19 +1806,19 @@
       <c r="D17" s="5"/>
       <c r="E17" s="3"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="9"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="5"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="10"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:19">
       <c r="A18" s="3"/>
@@ -1866,19 +1827,19 @@
       <c r="D18" s="5"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="9"/>
+      <c r="G18" s="8"/>
       <c r="H18" s="5"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="10"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:19">
       <c r="A19" s="3"/>
@@ -1887,19 +1848,19 @@
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="9"/>
+      <c r="G19" s="8"/>
       <c r="H19" s="5"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="10"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:19">
       <c r="A20" s="3"/>
@@ -1908,19 +1869,19 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="9"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="5"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V20">
